--- a/reports/valuation_results_2026-04-14.xlsx
+++ b/reports/valuation_results_2026-04-14.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taeoh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7413334-F588-4451-8411-322027E9BD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A17A3F5-FB8A-4BED-AE40-F9509283C1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10920" yWindow="2770" windowWidth="24980" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Valuation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -3298,50 +3309,50 @@
         <v>-9.08</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:15" s="16" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="13">
         <v>396500</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="13">
         <v>697841.66</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="12">
         <v>-43.18</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="12">
         <v>1.77</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="12">
         <v>8.2899999999999991</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="12">
         <v>23.02</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="12">
         <v>23.1</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="12">
         <v>19.59</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" s="12">
         <v>4</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" s="12">
         <v>0.36</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N26" s="4">
+      <c r="M26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" s="14">
         <v>36.74</v>
       </c>
-      <c r="O26" s="4">
+      <c r="O26" s="14">
         <v>0.63</v>
       </c>
     </row>
@@ -6046,49 +6057,49 @@
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="13">
         <v>12700</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="13">
         <v>28607.94</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="12">
         <v>-55.61</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="12">
         <v>0.79</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G85" s="12">
         <v>8.7100000000000009</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="12">
         <v>9.81</v>
       </c>
-      <c r="I85" s="2">
+      <c r="I85" s="12">
         <v>30.52</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85" s="12">
         <v>12.62</v>
       </c>
-      <c r="K85" s="2">
+      <c r="K85" s="12">
         <v>12.95</v>
       </c>
-      <c r="L85" s="2">
+      <c r="L85" s="12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N85" s="4">
+      <c r="M85" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" s="14">
         <v>341.79</v>
       </c>
-      <c r="O85" s="4">
+      <c r="O85" s="14">
         <v>-2.76</v>
       </c>
     </row>
